--- a/blog/downloads/cronograma-fisico-financeiro-modelo.xlsx
+++ b/blog/downloads/cronograma-fisico-financeiro-modelo.xlsx
@@ -204,6 +204,147 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Curva S — desembolso acumulado</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'FINANCEIRO'!$C$3:$T$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'FINANCEIRO'!$C$18:$T$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Mês</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% acumulado</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -585,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -758,7 +899,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Movimento de terra</t>
+          <t>Fundação</t>
         </is>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -787,7 +928,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Fundações</t>
+          <t>Estrutura</t>
         </is>
       </c>
       <c r="B6" s="10" t="n"/>
@@ -816,7 +957,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Estrutura</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -845,7 +986,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Vedações verticais</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="B8" s="10" t="n"/>
@@ -874,7 +1015,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -903,7 +1044,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Impermeabilizações</t>
+          <t>Instalações elétricas</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -932,7 +1073,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Instalações hidráulicas</t>
         </is>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -961,7 +1102,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Vidros e ferragens</t>
+          <t>Revestimentos</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -990,7 +1131,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Revest. internos</t>
+          <t>Pisos</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -1019,7 +1160,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Revest. externos</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="B14" s="10" t="n"/>
@@ -1048,7 +1189,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Forros</t>
+          <t>Limpeza final</t>
         </is>
       </c>
       <c r="B15" s="10" t="n"/>
@@ -1074,180 +1215,6 @@
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Pisos</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="10" t="n"/>
-      <c r="J16" s="10" t="n"/>
-      <c r="K16" s="10" t="n"/>
-      <c r="L16" s="10" t="n"/>
-      <c r="M16" s="10" t="n"/>
-      <c r="N16" s="10" t="n"/>
-      <c r="O16" s="10" t="n"/>
-      <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="10" t="n"/>
-      <c r="R16" s="10" t="n"/>
-      <c r="S16" s="10" t="n"/>
-      <c r="T16" s="11">
-        <f>IF(SUM(B16:S16)=0,"",SUM(B16:S16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Pinturas</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="n"/>
-      <c r="N17" s="10" t="n"/>
-      <c r="O17" s="10" t="n"/>
-      <c r="P17" s="10" t="n"/>
-      <c r="Q17" s="10" t="n"/>
-      <c r="R17" s="10" t="n"/>
-      <c r="S17" s="10" t="n"/>
-      <c r="T17" s="11">
-        <f>IF(SUM(B17:S17)=0,"",SUM(B17:S17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Inst. hidrossanitárias</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="10" t="n"/>
-      <c r="O18" s="10" t="n"/>
-      <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="10" t="n"/>
-      <c r="R18" s="10" t="n"/>
-      <c r="S18" s="10" t="n"/>
-      <c r="T18" s="11">
-        <f>IF(SUM(B18:S18)=0,"",SUM(B18:S18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Inst. elétricas</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="11">
-        <f>IF(SUM(B19:S19)=0,"",SUM(B19:S19))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>AVAC e exaustão</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="10" t="n"/>
-      <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="10" t="n"/>
-      <c r="R20" s="10" t="n"/>
-      <c r="S20" s="10" t="n"/>
-      <c r="T20" s="11">
-        <f>IF(SUM(B20:S20)=0,"",SUM(B20:S20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Complementares e limpeza</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="10" t="n"/>
-      <c r="N21" s="10" t="n"/>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="10" t="n"/>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="10" t="n"/>
-      <c r="T21" s="11">
-        <f>IF(SUM(B21:S21)=0,"",SUM(B21:S21))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1259,7 +1226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1483,7 +1450,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Movimento de terra</t>
+          <t>Fundação</t>
         </is>
       </c>
       <c r="B5" s="12" t="n"/>
@@ -1563,7 +1530,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Fundações</t>
+          <t>Estrutura</t>
         </is>
       </c>
       <c r="B6" s="12" t="n"/>
@@ -1643,7 +1610,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Estrutura</t>
+          <t>Alvenaria</t>
         </is>
       </c>
       <c r="B7" s="12" t="n"/>
@@ -1723,7 +1690,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Vedações verticais</t>
+          <t>Cobertura</t>
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -1803,7 +1770,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Cobertura</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="B9" s="12" t="n"/>
@@ -1883,7 +1850,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Impermeabilizações</t>
+          <t>Instalações elétricas</t>
         </is>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -1963,7 +1930,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Esquadrias</t>
+          <t>Instalações hidráulicas</t>
         </is>
       </c>
       <c r="B11" s="12" t="n"/>
@@ -2043,7 +2010,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Vidros e ferragens</t>
+          <t>Revestimentos</t>
         </is>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -2123,7 +2090,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Revest. internos</t>
+          <t>Pisos</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
@@ -2203,7 +2170,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Revest. externos</t>
+          <t>Pintura</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -2283,7 +2250,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Forros</t>
+          <t>Limpeza final</t>
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
@@ -2361,734 +2328,255 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Pisos</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!B16)</f>
-        <v/>
-      </c>
-      <c r="D16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!C16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!D16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!E16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!F16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!H16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!I16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!J16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!K16)</f>
-        <v/>
-      </c>
-      <c r="M16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!L16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!M16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!N16)</f>
-        <v/>
-      </c>
-      <c r="P16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!O16)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!P16)</f>
-        <v/>
-      </c>
-      <c r="R16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!Q16)</f>
-        <v/>
-      </c>
-      <c r="S16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!R16)</f>
-        <v/>
-      </c>
-      <c r="T16" s="13">
-        <f>IF($B16="","",$B16*FÍSICO!S16)</f>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>DESEMBOLSO DO MÊS</t>
+        </is>
+      </c>
+      <c r="B16" s="15">
+        <f>SUM(B4:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="15">
+        <f>SUM(C4:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>SUM(D4:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>SUM(E4:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
+        <f>SUM(F4:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="15">
+        <f>SUM(G4:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="15">
+        <f>SUM(H4:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="15">
+        <f>SUM(I4:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="15">
+        <f>SUM(J4:J15)</f>
+        <v/>
+      </c>
+      <c r="K16" s="15">
+        <f>SUM(K4:K15)</f>
+        <v/>
+      </c>
+      <c r="L16" s="15">
+        <f>SUM(L4:L15)</f>
+        <v/>
+      </c>
+      <c r="M16" s="15">
+        <f>SUM(M4:M15)</f>
+        <v/>
+      </c>
+      <c r="N16" s="15">
+        <f>SUM(N4:N15)</f>
+        <v/>
+      </c>
+      <c r="O16" s="15">
+        <f>SUM(O4:O15)</f>
+        <v/>
+      </c>
+      <c r="P16" s="15">
+        <f>SUM(P4:P15)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="15">
+        <f>SUM(Q4:Q15)</f>
+        <v/>
+      </c>
+      <c r="R16" s="15">
+        <f>SUM(R4:R15)</f>
+        <v/>
+      </c>
+      <c r="S16" s="15">
+        <f>SUM(S4:S15)</f>
+        <v/>
+      </c>
+      <c r="T16" s="15">
+        <f>SUM(T4:T15)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Pinturas</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!B17)</f>
-        <v/>
-      </c>
-      <c r="D17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!C17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!D17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!E17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!F17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!G17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!H17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!I17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!J17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!K17)</f>
-        <v/>
-      </c>
-      <c r="M17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!L17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!M17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!N17)</f>
-        <v/>
-      </c>
-      <c r="P17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!O17)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!P17)</f>
-        <v/>
-      </c>
-      <c r="R17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!Q17)</f>
-        <v/>
-      </c>
-      <c r="S17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!R17)</f>
-        <v/>
-      </c>
-      <c r="T17" s="13">
-        <f>IF($B17="","",$B17*FÍSICO!S17)</f>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>ACUMULADO</t>
+        </is>
+      </c>
+      <c r="C17" s="16">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f>C17+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f>D17+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
+        <f>E17+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="16">
+        <f>F17+G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="16">
+        <f>G17+H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="16">
+        <f>H17+I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="16">
+        <f>I17+J16</f>
+        <v/>
+      </c>
+      <c r="K17" s="16">
+        <f>J17+K16</f>
+        <v/>
+      </c>
+      <c r="L17" s="16">
+        <f>K17+L16</f>
+        <v/>
+      </c>
+      <c r="M17" s="16">
+        <f>L17+M16</f>
+        <v/>
+      </c>
+      <c r="N17" s="16">
+        <f>M17+N16</f>
+        <v/>
+      </c>
+      <c r="O17" s="16">
+        <f>N17+O16</f>
+        <v/>
+      </c>
+      <c r="P17" s="16">
+        <f>O17+P16</f>
+        <v/>
+      </c>
+      <c r="Q17" s="16">
+        <f>P17+Q16</f>
+        <v/>
+      </c>
+      <c r="R17" s="16">
+        <f>Q17+R16</f>
+        <v/>
+      </c>
+      <c r="S17" s="16">
+        <f>R17+S16</f>
+        <v/>
+      </c>
+      <c r="T17" s="16">
+        <f>S17+T16</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Inst. hidrossanitárias</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!B18)</f>
-        <v/>
-      </c>
-      <c r="D18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!C18)</f>
-        <v/>
-      </c>
-      <c r="E18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!D18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!F18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!H18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!I18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!J18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!K18)</f>
-        <v/>
-      </c>
-      <c r="M18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!L18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!M18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!N18)</f>
-        <v/>
-      </c>
-      <c r="P18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!O18)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!P18)</f>
-        <v/>
-      </c>
-      <c r="R18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!Q18)</f>
-        <v/>
-      </c>
-      <c r="S18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!R18)</f>
-        <v/>
-      </c>
-      <c r="T18" s="13">
-        <f>IF($B18="","",$B18*FÍSICO!S18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Inst. elétricas</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!B19)</f>
-        <v/>
-      </c>
-      <c r="D19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!C19)</f>
-        <v/>
-      </c>
-      <c r="E19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!D19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!E19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!F19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!H19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!I19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!J19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!K19)</f>
-        <v/>
-      </c>
-      <c r="M19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!L19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!M19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!N19)</f>
-        <v/>
-      </c>
-      <c r="P19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!O19)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!P19)</f>
-        <v/>
-      </c>
-      <c r="R19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!Q19)</f>
-        <v/>
-      </c>
-      <c r="S19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!R19)</f>
-        <v/>
-      </c>
-      <c r="T19" s="13">
-        <f>IF($B19="","",$B19*FÍSICO!S19)</f>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>% ACUMULADO (curva S)</t>
+        </is>
+      </c>
+      <c r="C18" s="17">
+        <f>IF($B16=0,"",C17/$B16)</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>IF($B16=0,"",D17/$B16)</f>
+        <v/>
+      </c>
+      <c r="E18" s="17">
+        <f>IF($B16=0,"",E17/$B16)</f>
+        <v/>
+      </c>
+      <c r="F18" s="17">
+        <f>IF($B16=0,"",F17/$B16)</f>
+        <v/>
+      </c>
+      <c r="G18" s="17">
+        <f>IF($B16=0,"",G17/$B16)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17">
+        <f>IF($B16=0,"",H17/$B16)</f>
+        <v/>
+      </c>
+      <c r="I18" s="17">
+        <f>IF($B16=0,"",I17/$B16)</f>
+        <v/>
+      </c>
+      <c r="J18" s="17">
+        <f>IF($B16=0,"",J17/$B16)</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>IF($B16=0,"",K17/$B16)</f>
+        <v/>
+      </c>
+      <c r="L18" s="17">
+        <f>IF($B16=0,"",L17/$B16)</f>
+        <v/>
+      </c>
+      <c r="M18" s="17">
+        <f>IF($B16=0,"",M17/$B16)</f>
+        <v/>
+      </c>
+      <c r="N18" s="17">
+        <f>IF($B16=0,"",N17/$B16)</f>
+        <v/>
+      </c>
+      <c r="O18" s="17">
+        <f>IF($B16=0,"",O17/$B16)</f>
+        <v/>
+      </c>
+      <c r="P18" s="17">
+        <f>IF($B16=0,"",P17/$B16)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="17">
+        <f>IF($B16=0,"",Q17/$B16)</f>
+        <v/>
+      </c>
+      <c r="R18" s="17">
+        <f>IF($B16=0,"",R17/$B16)</f>
+        <v/>
+      </c>
+      <c r="S18" s="17">
+        <f>IF($B16=0,"",S17/$B16)</f>
+        <v/>
+      </c>
+      <c r="T18" s="17">
+        <f>IF($B16=0,"",T17/$B16)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>AVAC e exaustão</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!B20)</f>
-        <v/>
-      </c>
-      <c r="D20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!C20)</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!D20)</f>
-        <v/>
-      </c>
-      <c r="F20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!E20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!F20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!H20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!I20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!J20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!K20)</f>
-        <v/>
-      </c>
-      <c r="M20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!L20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!M20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!N20)</f>
-        <v/>
-      </c>
-      <c r="P20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!O20)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!P20)</f>
-        <v/>
-      </c>
-      <c r="R20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!Q20)</f>
-        <v/>
-      </c>
-      <c r="S20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!R20)</f>
-        <v/>
-      </c>
-      <c r="T20" s="13">
-        <f>IF($B20="","",$B20*FÍSICO!S20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Complementares e limpeza</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!B21)</f>
-        <v/>
-      </c>
-      <c r="D21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!C21)</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!D21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!E21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!F21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!H21)</f>
-        <v/>
-      </c>
-      <c r="J21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!I21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!J21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!K21)</f>
-        <v/>
-      </c>
-      <c r="M21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!L21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!M21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!N21)</f>
-        <v/>
-      </c>
-      <c r="P21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!O21)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!P21)</f>
-        <v/>
-      </c>
-      <c r="R21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!Q21)</f>
-        <v/>
-      </c>
-      <c r="S21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!R21)</f>
-        <v/>
-      </c>
-      <c r="T21" s="13">
-        <f>IF($B21="","",$B21*FÍSICO!S21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>DESEMBOLSO DO MÊS</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <f>SUM(B4:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="15">
-        <f>SUM(C4:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="15">
-        <f>SUM(D4:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="15">
-        <f>SUM(E4:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="15">
-        <f>SUM(F4:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="15">
-        <f>SUM(G4:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="15">
-        <f>SUM(H4:H21)</f>
-        <v/>
-      </c>
-      <c r="I22" s="15">
-        <f>SUM(I4:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="15">
-        <f>SUM(J4:J21)</f>
-        <v/>
-      </c>
-      <c r="K22" s="15">
-        <f>SUM(K4:K21)</f>
-        <v/>
-      </c>
-      <c r="L22" s="15">
-        <f>SUM(L4:L21)</f>
-        <v/>
-      </c>
-      <c r="M22" s="15">
-        <f>SUM(M4:M21)</f>
-        <v/>
-      </c>
-      <c r="N22" s="15">
-        <f>SUM(N4:N21)</f>
-        <v/>
-      </c>
-      <c r="O22" s="15">
-        <f>SUM(O4:O21)</f>
-        <v/>
-      </c>
-      <c r="P22" s="15">
-        <f>SUM(P4:P21)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="15">
-        <f>SUM(Q4:Q21)</f>
-        <v/>
-      </c>
-      <c r="R22" s="15">
-        <f>SUM(R4:R21)</f>
-        <v/>
-      </c>
-      <c r="S22" s="15">
-        <f>SUM(S4:S21)</f>
-        <v/>
-      </c>
-      <c r="T22" s="15">
-        <f>SUM(T4:T21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>ACUMULADO</t>
-        </is>
-      </c>
-      <c r="C23" s="16">
-        <f>C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="16">
-        <f>C23+D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="16">
-        <f>D23+E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="16">
-        <f>E23+F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="16">
-        <f>F23+G22</f>
-        <v/>
-      </c>
-      <c r="H23" s="16">
-        <f>G23+H22</f>
-        <v/>
-      </c>
-      <c r="I23" s="16">
-        <f>H23+I22</f>
-        <v/>
-      </c>
-      <c r="J23" s="16">
-        <f>I23+J22</f>
-        <v/>
-      </c>
-      <c r="K23" s="16">
-        <f>J23+K22</f>
-        <v/>
-      </c>
-      <c r="L23" s="16">
-        <f>K23+L22</f>
-        <v/>
-      </c>
-      <c r="M23" s="16">
-        <f>L23+M22</f>
-        <v/>
-      </c>
-      <c r="N23" s="16">
-        <f>M23+N22</f>
-        <v/>
-      </c>
-      <c r="O23" s="16">
-        <f>N23+O22</f>
-        <v/>
-      </c>
-      <c r="P23" s="16">
-        <f>O23+P22</f>
-        <v/>
-      </c>
-      <c r="Q23" s="16">
-        <f>P23+Q22</f>
-        <v/>
-      </c>
-      <c r="R23" s="16">
-        <f>Q23+R22</f>
-        <v/>
-      </c>
-      <c r="S23" s="16">
-        <f>R23+S22</f>
-        <v/>
-      </c>
-      <c r="T23" s="16">
-        <f>S23+T22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>% ACUMULADO (curva S)</t>
-        </is>
-      </c>
-      <c r="C24" s="17">
-        <f>IF($B22=0,"",C23/$B22)</f>
-        <v/>
-      </c>
-      <c r="D24" s="17">
-        <f>IF($B22=0,"",D23/$B22)</f>
-        <v/>
-      </c>
-      <c r="E24" s="17">
-        <f>IF($B22=0,"",E23/$B22)</f>
-        <v/>
-      </c>
-      <c r="F24" s="17">
-        <f>IF($B22=0,"",F23/$B22)</f>
-        <v/>
-      </c>
-      <c r="G24" s="17">
-        <f>IF($B22=0,"",G23/$B22)</f>
-        <v/>
-      </c>
-      <c r="H24" s="17">
-        <f>IF($B22=0,"",H23/$B22)</f>
-        <v/>
-      </c>
-      <c r="I24" s="17">
-        <f>IF($B22=0,"",I23/$B22)</f>
-        <v/>
-      </c>
-      <c r="J24" s="17">
-        <f>IF($B22=0,"",J23/$B22)</f>
-        <v/>
-      </c>
-      <c r="K24" s="17">
-        <f>IF($B22=0,"",K23/$B22)</f>
-        <v/>
-      </c>
-      <c r="L24" s="17">
-        <f>IF($B22=0,"",L23/$B22)</f>
-        <v/>
-      </c>
-      <c r="M24" s="17">
-        <f>IF($B22=0,"",M23/$B22)</f>
-        <v/>
-      </c>
-      <c r="N24" s="17">
-        <f>IF($B22=0,"",N23/$B22)</f>
-        <v/>
-      </c>
-      <c r="O24" s="17">
-        <f>IF($B22=0,"",O23/$B22)</f>
-        <v/>
-      </c>
-      <c r="P24" s="17">
-        <f>IF($B22=0,"",P23/$B22)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="17">
-        <f>IF($B22=0,"",Q23/$B22)</f>
-        <v/>
-      </c>
-      <c r="R24" s="17">
-        <f>IF($B22=0,"",R23/$B22)</f>
-        <v/>
-      </c>
-      <c r="S24" s="17">
-        <f>IF($B22=0,"",S23/$B22)</f>
-        <v/>
-      </c>
-      <c r="T24" s="17">
-        <f>IF($B22=0,"",T23/$B22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Selecione a linha "% ACUMULADO" e insira um gráfico de linhas: é a curva S da obra.</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>A curva S abaixo se preenche sozinha conforme você lança os valores e o avanço físico.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>